--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,8 +86,8 @@
   <si>
     <t>IHE-PaLM - Laboratory Specialty Section
  - Une section de premier niveau est appelée 'Chapitre' et correspond à une sous-discipline de la biologie médicale (par exemple « biochimie »). Elle contient :
-  - soit directement la présentation des résultats d'examens de biologie médicale obtenus pour ce chapitre : dans ce cas, il y a un unique élément &lt;text&gt; (présentation du contenu pour le lecteur) et un unique élément &lt;entry&gt; (données codées pour les SIS dont procède le contenu de l'élément &lt;text&gt;)
-  - soit une liste de sections de second niveau, appelés sous-chapitres (par exemple « Gaz du sang ») : dans ce cas, il y a une liste d'éléments &lt;component&gt; dont chacun introduit une &lt;section&gt; de second niveau présentant un sous-ensemble de un ou plusieurs résultats d'examens de biologie médicale.Remarque : L'arborescence du corps du compte rendu d'examens de biologie médicale est choisie par le LPS producteur du document selon la logique de présentation définie par le laboratoire.</t>
+  - soit directement la présentation des résultats d'examens de biologie médicale obtenus pour ce chapitre : dans ce cas, il y a un unique élément `&lt;text&gt;` (présentation du contenu pour le lecteur) et un unique élément `&lt;entry&gt;` (données codées pour les SIS dont procède le contenu de l'élément `&lt;text&gt;`)
+  - soit une liste de sections de second niveau, appelés sous-chapitres (par exemple « Gaz du sang ») : dans ce cas, il y a une liste d'éléments `&lt;component&gt;` dont chacun introduit une `&lt;section&gt;` de second niveau présentant un sous-ensemble de un ou plusieurs résultats d'examens de biologie médicale.Remarque : L'arborescence du corps du compte rendu d'examens de biologie médicale est choisie par le LPS producteur du document selon la logique de présentation définie par le laboratoire.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-cr-bio-chapitre.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
